--- a/artfynd/A 24185-2025 artfynd.xlsx
+++ b/artfynd/A 24185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81741341</v>
+        <v>87028202</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjoarvekjåhkå2, Lu lm</t>
+          <t>En route, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>784516.2376189097</v>
+        <v>784071</v>
       </c>
       <c r="R2" t="n">
-        <v>7378109.954257915</v>
+        <v>7378267</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,76 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Agneta Olsson</t>
+          <t>Mathias Molau</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Agneta Olsson, Otilia Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>BiotopkarteringBD</t>
-        </is>
-      </c>
+          <t>Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81741337</v>
+        <v>87028203</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjoarvekjåhkå2, Lu lm</t>
+          <t>En route, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>784516.2376189097</v>
+        <v>784125</v>
       </c>
       <c r="R3" t="n">
-        <v>7378109.954257915</v>
+        <v>7378259</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,72 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Agneta Olsson</t>
+          <t>Mathias Molau</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Agneta Olsson, Otilia Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>BiotopkarteringBD</t>
-        </is>
-      </c>
+          <t>Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81741140</v>
+        <v>87028204</v>
       </c>
       <c r="B4" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjoarvekjåhkå2, Lu lm</t>
+          <t>En route, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784516.2376189097</v>
+        <v>784067</v>
       </c>
       <c r="R4" t="n">
-        <v>7378109.954257915</v>
+        <v>7378250</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-07-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,76 +948,69 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Agneta Olsson</t>
+          <t>Mathias Molau</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Agneta Olsson, Otilia Johansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>BiotopkarteringBD</t>
-        </is>
-      </c>
+          <t>Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87028204</v>
+        <v>81741140</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>En route, Lu lm</t>
+          <t>Tjoarvekjåhkå2, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>784066.8772951388</v>
+        <v>784516</v>
       </c>
       <c r="R5" t="n">
-        <v>7378249.993005296</v>
+        <v>7378110</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,22 +1034,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,68 +1048,78 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mathias Molau</t>
+          <t>Agneta Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mathias Molau</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Agneta Olsson, Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>BiotopkarteringBD</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87028202</v>
+        <v>81741341</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>En route, Lu lm</t>
+          <t>Tjoarvekjåhkå2, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>784071.1996735838</v>
+        <v>784516</v>
       </c>
       <c r="R6" t="n">
-        <v>7378266.977415317</v>
+        <v>7378110</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,22 +1146,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,62 +1166,71 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mathias Molau</t>
+          <t>Agneta Olsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mathias Molau</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Agneta Olsson, Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>BiotopkarteringBD</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>87028203</v>
+        <v>81741337</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>En route, Lu lm</t>
+          <t>Tjoarvekjåhkå2, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784124.9120933951</v>
+        <v>784516</v>
       </c>
       <c r="R7" t="n">
-        <v>7378259.154252693</v>
+        <v>7378110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,22 +1257,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1277,125 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mathias Molau</t>
+          <t>Agneta Olsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mathias Molau</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Agneta Olsson, Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>BiotopkarteringBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>81741120</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tjoarvekjåhkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>784502</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7378143</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-07-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Agneta Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Agneta Olsson, Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>BiotopkarteringBD</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24185-2025 artfynd.xlsx
+++ b/artfynd/A 24185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87028202</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87028203</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87028204</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
           <t>BiotopkarteringBD</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81741140</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
           <t>BiotopkarteringBD</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81741341</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>BiotopkarteringBD</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81741337</t>
         </is>
       </c>
     </row>
@@ -1396,8 +1431,22 @@
           <t>BiotopkarteringBD</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81741120</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>